--- a/output/graficos_dimensiones/comunal_d_env_a_2018_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:14</t>
+    <t xml:space="preserve">2026-09-10 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:28</t>
+    <t xml:space="preserve">2026-09-12 22:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_antofagasta.xlsx
@@ -45,12 +45,12 @@
     <t xml:space="preserve">Mejillones</t>
   </si>
   <si>
+    <t xml:space="preserve">María Elena</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ollagüe</t>
   </si>
   <si>
-    <t xml:space="preserve">María Elena</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calama</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:39</t>
+    <t xml:space="preserve">2026-09-24 00:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>68.98</v>
+        <v>73.29</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         <v>2018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>68.48</v>
+        <v>72.87</v>
       </c>
     </row>
     <row r="4">
@@ -536,7 +536,7 @@
         <v>2018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>56.97</v>
+        <v>60.72</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         <v>2018</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>51.43</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="6">
@@ -564,13 +564,13 @@
         <v>9</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2202</v>
+        <v>2302</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>48</v>
+        <v>51.07</v>
       </c>
     </row>
     <row r="7">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2302</v>
+        <v>2202</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>47.65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -604,7 +604,7 @@
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46.37</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         <v>2018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>38.75</v>
+        <v>41.23</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         <v>2018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>31.03</v>
+        <v>32.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:08</t>
+    <t xml:space="preserve">2026-10-02 15:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:37</t>
+    <t xml:space="preserve">2026-10-05 16:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
